--- a/back end/energy_info.xlsx
+++ b/back end/energy_info.xlsx
@@ -1,46 +1,148 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\[업무]\에너지관리\back end\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E997B761-226F-42C6-A006-08D478CCCA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="EnergyInfo" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+  <si>
+    <t>시설명</t>
+  </si>
+  <si>
+    <t>에너지종류</t>
+  </si>
+  <si>
+    <t>고객번호</t>
+  </si>
+  <si>
+    <t>금융기관</t>
+  </si>
+  <si>
+    <t>계좌번호</t>
+  </si>
+  <si>
+    <t>울주군립야영장(별빛)</t>
+  </si>
+  <si>
+    <t>상하수도</t>
+  </si>
+  <si>
+    <t>2016601258</t>
+  </si>
+  <si>
+    <t>농협</t>
+  </si>
+  <si>
+    <t>124-0016-4342-002</t>
+  </si>
+  <si>
+    <t>울주군립야영장(등억)</t>
+  </si>
+  <si>
+    <t>2018600854</t>
+  </si>
+  <si>
+    <t>124-0016-4502-363</t>
+  </si>
+  <si>
+    <t>울주군립야영장(달빛)</t>
+  </si>
+  <si>
+    <t>2020600029</t>
+  </si>
+  <si>
+    <t>124-0016-4557-759</t>
+  </si>
+  <si>
+    <t>울주군립야영장(대운산)</t>
+  </si>
+  <si>
+    <t>통신</t>
+  </si>
+  <si>
+    <t>90045227663</t>
+  </si>
+  <si>
+    <t>790321-43-433684</t>
+  </si>
+  <si>
+    <t>전기</t>
+  </si>
+  <si>
+    <t>04-3972-6058</t>
+  </si>
+  <si>
+    <t>108535-64-518198</t>
+  </si>
+  <si>
+    <t>04-3963-0865</t>
+  </si>
+  <si>
+    <t>790058-35-262194</t>
+  </si>
+  <si>
+    <t>울주군립야영장(별빛, 확장)</t>
+  </si>
+  <si>
+    <t>04-3963-0883</t>
+  </si>
+  <si>
+    <t>790058-35-498591</t>
+  </si>
+  <si>
+    <t>울주군립야영장(주차장)</t>
+  </si>
+  <si>
+    <t>04-3752-0434</t>
+  </si>
+  <si>
+    <t>790058-37-693226</t>
+  </si>
+  <si>
+    <t>울주군립야영장(별빛, 주차장)</t>
+  </si>
+  <si>
+    <t>04 3752 0434</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -68,10 +170,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,182 +506,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>시설명</v>
-      </c>
-      <c r="B1" t="str">
-        <v>에너지종류</v>
-      </c>
-      <c r="C1" t="str">
-        <v>고객번호</v>
-      </c>
-      <c r="D1" t="str">
-        <v>금융기관</v>
-      </c>
-      <c r="E1" t="str">
-        <v>계좌번호</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>울주군립야영장(별빛)</v>
-      </c>
-      <c r="B2" t="str">
-        <v>상하수도</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2016601258</v>
-      </c>
-      <c r="D2" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E2" t="str">
-        <v>124-0016-4342-002</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>울주군립야영장(등억)</v>
-      </c>
-      <c r="B3" t="str">
-        <v>상하수도</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2018600854</v>
-      </c>
-      <c r="D3" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E3" t="str">
-        <v>124-0016-4502-363</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>울주군립야영장(달빛)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>상하수도</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2020600029</v>
-      </c>
-      <c r="D4" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E4" t="str">
-        <v>124-0016-4557-759</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>울주군립야영장(대운산)</v>
-      </c>
-      <c r="B5" t="str">
-        <v>통신</v>
-      </c>
-      <c r="C5" t="str">
-        <v>90045227663</v>
-      </c>
-      <c r="D5" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E5" t="str">
-        <v>790321-43-433684</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>울주군립야영장(등억)</v>
-      </c>
-      <c r="B6" t="str">
-        <v>전기</v>
-      </c>
-      <c r="C6" t="str">
-        <v>04-3972-6058</v>
-      </c>
-      <c r="D6" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E6" t="str">
-        <v>108535-64-518198</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>울주군립야영장(달빛)</v>
-      </c>
-      <c r="B7" t="str">
-        <v>전기</v>
-      </c>
-      <c r="C7" t="str">
-        <v>04-3963-0865</v>
-      </c>
-      <c r="D7" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E7" t="str">
-        <v>790058-35-262194</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>울주군립야영장(별빛, 확장)</v>
-      </c>
-      <c r="B8" t="str">
-        <v>전기</v>
-      </c>
-      <c r="C8" t="str">
-        <v>04-3963-0883</v>
-      </c>
-      <c r="D8" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E8" t="str">
-        <v>790058-35-498591</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>울주군립야영장(주차장)</v>
-      </c>
-      <c r="B9" t="str">
-        <v>전기</v>
-      </c>
-      <c r="C9" t="str">
-        <v>04-3752-0434</v>
-      </c>
-      <c r="D9" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E9" t="str">
-        <v>790058-37-693226</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>울주군립야영장(별빛, 주차장)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>전기</v>
-      </c>
-      <c r="C10" t="str">
-        <v>04 3752 0434</v>
-      </c>
-      <c r="D10" t="str">
-        <v>농협</v>
-      </c>
-      <c r="E10" t="str">
-        <v>790058-37-693226</v>
+    <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
+    <ignoredError sqref="A1:E10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>